--- a/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 2,57</t>
+          <t>-2,25; 2,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 5,59</t>
+          <t>-1,1; 5,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,62</t>
+          <t>-2,64; 3,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,19</t>
+          <t>-5,01; 2,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,62; 62,79</t>
+          <t>-35,73; 57,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,84; 71,7</t>
+          <t>-12,1; 67,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 49,37</t>
+          <t>-26,49; 50,11</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-30,53; 16,8</t>
+          <t>-29,75; 17,76</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 3,24</t>
+          <t>-1,84; 3,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,84; 5,07</t>
+          <t>-0,73; 4,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 4,79</t>
+          <t>-0,41; 4,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 11,22</t>
+          <t>0,53; 10,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 53,91</t>
+          <t>-22,92; 53,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 59,25</t>
+          <t>-6,62; 58,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 87,84</t>
+          <t>-5,61; 77,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,62; 183,22</t>
+          <t>3,52; 166,1</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,79</t>
+          <t>-1,14; 4,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 4,72</t>
+          <t>-1,62; 4,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,99</t>
+          <t>0,09; 4,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 48,25</t>
+          <t>-1,95; 54,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 88,66</t>
+          <t>-14,65; 83,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,79; 66,28</t>
+          <t>-16,28; 69,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 150,59</t>
+          <t>-0,42; 149,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 359,88</t>
+          <t>-11,78; 423,81</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,14</t>
+          <t>-0,01; 4,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 5,26</t>
+          <t>-0,62; 5,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 3,95</t>
+          <t>-1,5; 4,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,65</t>
+          <t>-3,35; 2,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 84,33</t>
+          <t>-0,33; 82,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 61,53</t>
+          <t>-5,65; 61,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 54,27</t>
+          <t>-14,33; 59,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 25,29</t>
+          <t>-25,29; 26,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,69</t>
+          <t>0,0; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,55</t>
+          <t>0,59; 3,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,92</t>
+          <t>0,35; 3,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 20,58</t>
+          <t>0,26; 21,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 44,83</t>
+          <t>-0,0; 44,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 41,62</t>
+          <t>5,91; 40,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,3; 46,53</t>
+          <t>4,5; 47,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 191,86</t>
+          <t>1,94; 181,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>0,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-7,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,39</t>
+          <t>-2,29; 2,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,36</t>
+          <t>-1,08; 5,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 3,53</t>
+          <t>-2,51; 3,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 2,11</t>
+          <t>-3,17; 3,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-35,73; 57,33</t>
+          <t>-35,57; 56,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,1; 67,74</t>
+          <t>-10,17; 70,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 50,11</t>
+          <t>-25,37; 45,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-29,75; 17,76</t>
+          <t>-19,46; 30,0</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,6</t>
+          <t>1,77</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,13</t>
+          <t>-1,97; 2,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,84</t>
+          <t>-0,68; 5,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,53</t>
+          <t>-0,43; 4,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 10,87</t>
+          <t>-1,08; 4,75</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 53,27</t>
+          <t>-23,18; 50,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 58,21</t>
+          <t>-6,07; 61,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 77,99</t>
+          <t>-6,02; 80,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 166,1</t>
+          <t>-6,83; 39,2</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,99</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>116,01%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,55</t>
+          <t>-1,19; 4,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 4,77</t>
+          <t>-1,63; 4,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 4,98</t>
+          <t>0,03; 5,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 54,78</t>
+          <t>-3,14; 4,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-14,65; 83,86</t>
+          <t>-15,31; 80,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,28; 69,65</t>
+          <t>-17,45; 69,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 149,38</t>
+          <t>0,54; 160,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 423,81</t>
+          <t>-18,48; 32,42</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,87%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 4,99</t>
+          <t>0,31; 5,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,26</t>
+          <t>-0,77; 4,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,06</t>
+          <t>-1,51; 4,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 2,72</t>
+          <t>-1,57; 3,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 82,57</t>
+          <t>3,32; 88,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 61,92</t>
+          <t>-7,22; 56,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,33; 59,72</t>
+          <t>-15,21; 60,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,29; 26,79</t>
+          <t>-12,31; 33,95</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,71</t>
+          <t>0,96</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,65</t>
+          <t>0,15; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,59; 3,53</t>
+          <t>0,43; 3,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,02</t>
+          <t>0,46; 3,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,26; 21,7</t>
+          <t>-0,6; 2,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 44,34</t>
+          <t>1,9; 45,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 40,93</t>
+          <t>4,09; 41,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,5; 47,37</t>
+          <t>6,53; 48,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 181,22</t>
+          <t>-4,1; 18,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2A_lim_R-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
